--- a/artfynd/A 47782-2025 artfynd.xlsx
+++ b/artfynd/A 47782-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129405582</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47782-2025 artfynd.xlsx
+++ b/artfynd/A 47782-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129405582</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,6 +814,996 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129726549</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sirbohult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>465417</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6548809</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska spår på tall</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129726544</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sirbohult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>465494</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6548857</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska spår på tall</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129726345</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sirbohult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>465392</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6548988</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129726545</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sirbohult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>465543</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6548619</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska spår på tall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129726550</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sirbohult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>465362</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6549140</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska spår på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129726548</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sirbohult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>465482</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6548524</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska spår på tall</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129726546</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sirbohult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>465546</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6548446</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska spår på tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129726348</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sirbohult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>465501</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6548842</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska spår på tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129726547</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sirbohult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>465507</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6548548</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska spår på tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47782-2025 artfynd.xlsx
+++ b/artfynd/A 47782-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129405582</v>
       </c>
       <c r="B2" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>129726549</v>
       </c>
       <c r="B3" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>129726544</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>129726345</v>
       </c>
       <c r="B5" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>129726545</v>
       </c>
       <c r="B6" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129726550</v>
       </c>
       <c r="B7" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>129726548</v>
       </c>
       <c r="B8" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>129726546</v>
       </c>
       <c r="B9" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129726348</v>
+        <v>129726547</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465501</v>
+        <v>465507</v>
       </c>
       <c r="R10" t="n">
-        <v>6548842</v>
+        <v>6548548</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1697,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726547</v>
+        <v>129726348</v>
       </c>
       <c r="B11" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465507</v>
+        <v>465501</v>
       </c>
       <c r="R11" t="n">
-        <v>6548548</v>
+        <v>6548842</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1804,6 +1804,138 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129767860</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>465528</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6548493</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack med savflöde</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47782-2025 artfynd.xlsx
+++ b/artfynd/A 47782-2025 artfynd.xlsx
@@ -1587,7 +1587,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129726547</v>
+        <v>129726348</v>
       </c>
       <c r="B10" t="n">
         <v>57736</v>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465507</v>
+        <v>465501</v>
       </c>
       <c r="R10" t="n">
-        <v>6548548</v>
+        <v>6548842</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1697,7 +1697,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726348</v>
+        <v>129726547</v>
       </c>
       <c r="B11" t="n">
         <v>57736</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465501</v>
+        <v>465507</v>
       </c>
       <c r="R11" t="n">
-        <v>6548842</v>
+        <v>6548548</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 47782-2025 artfynd.xlsx
+++ b/artfynd/A 47782-2025 artfynd.xlsx
@@ -1587,7 +1587,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129726348</v>
+        <v>129726547</v>
       </c>
       <c r="B10" t="n">
         <v>57736</v>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465501</v>
+        <v>465507</v>
       </c>
       <c r="R10" t="n">
-        <v>6548842</v>
+        <v>6548548</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1697,7 +1697,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726547</v>
+        <v>129726348</v>
       </c>
       <c r="B11" t="n">
         <v>57736</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465507</v>
+        <v>465501</v>
       </c>
       <c r="R11" t="n">
-        <v>6548548</v>
+        <v>6548842</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 47782-2025 artfynd.xlsx
+++ b/artfynd/A 47782-2025 artfynd.xlsx
@@ -1810,7 +1810,7 @@
         <v>129767860</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47782-2025 artfynd.xlsx
+++ b/artfynd/A 47782-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>129726549</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>129726544</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>129726345</v>
       </c>
       <c r="B5" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>129726545</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129726550</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>129726548</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>129726546</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129726547</v>
+        <v>129726348</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465507</v>
+        <v>465501</v>
       </c>
       <c r="R10" t="n">
-        <v>6548548</v>
+        <v>6548842</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1697,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726348</v>
+        <v>129726547</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465501</v>
+        <v>465507</v>
       </c>
       <c r="R11" t="n">
-        <v>6548842</v>
+        <v>6548548</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 47782-2025 artfynd.xlsx
+++ b/artfynd/A 47782-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>129726549</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>129726544</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>129726345</v>
       </c>
       <c r="B5" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>129726545</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129726550</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>129726548</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>129726546</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>129726348</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>129726547</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>129767860</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47782-2025 artfynd.xlsx
+++ b/artfynd/A 47782-2025 artfynd.xlsx
@@ -1587,7 +1587,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129726348</v>
+        <v>129726547</v>
       </c>
       <c r="B10" t="n">
         <v>57740</v>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465501</v>
+        <v>465507</v>
       </c>
       <c r="R10" t="n">
-        <v>6548842</v>
+        <v>6548548</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1697,7 +1697,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726547</v>
+        <v>129726348</v>
       </c>
       <c r="B11" t="n">
         <v>57740</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465507</v>
+        <v>465501</v>
       </c>
       <c r="R11" t="n">
-        <v>6548548</v>
+        <v>6548842</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 47782-2025 artfynd.xlsx
+++ b/artfynd/A 47782-2025 artfynd.xlsx
@@ -1040,7 +1040,7 @@
         <v>129726345</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47782-2025 artfynd.xlsx
+++ b/artfynd/A 47782-2025 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>129405582</v>
       </c>
       <c r="B2" t="n">
-        <v>57733</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -817,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129726549</v>
+        <v>129726348</v>
       </c>
       <c r="B3" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465417</v>
+        <v>465501</v>
       </c>
       <c r="R3" t="n">
-        <v>6548809</v>
+        <v>6548842</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -930,7 +930,7 @@
         <v>129726544</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129726345</v>
+        <v>129726545</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,7 +1070,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465392</v>
+        <v>465543</v>
       </c>
       <c r="R5" t="n">
-        <v>6548988</v>
+        <v>6548619</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Upprörd, varnande</t>
+          <t>Färska spår på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726545</v>
+        <v>129726546</v>
       </c>
       <c r="B6" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465543</v>
+        <v>465546</v>
       </c>
       <c r="R6" t="n">
-        <v>6548619</v>
+        <v>6548446</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726550</v>
+        <v>129726547</v>
       </c>
       <c r="B7" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465362</v>
+        <v>465507</v>
       </c>
       <c r="R7" t="n">
-        <v>6549140</v>
+        <v>6548548</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1370,7 +1370,7 @@
         <v>129726548</v>
       </c>
       <c r="B8" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129726546</v>
+        <v>129726549</v>
       </c>
       <c r="B9" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465546</v>
+        <v>465417</v>
       </c>
       <c r="R9" t="n">
-        <v>6548446</v>
+        <v>6548809</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129726547</v>
+        <v>129726550</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465507</v>
+        <v>465362</v>
       </c>
       <c r="R10" t="n">
-        <v>6548548</v>
+        <v>6549140</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1697,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726348</v>
+        <v>129767860</v>
       </c>
       <c r="B11" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,27 +1726,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sirbohult, Nrk</t>
+          <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465501</v>
+        <v>465528</v>
       </c>
       <c r="R11" t="n">
-        <v>6548842</v>
+        <v>6548493</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1770,17 +1767,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska spår på tall</t>
+          <t>Ringhack med savflöde</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,26 +1798,41 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129767860</v>
+        <v>129726345</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,42 +1840,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
+          <t>Sirbohult, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465528</v>
+        <v>465392</v>
       </c>
       <c r="R12" t="n">
-        <v>6548493</v>
+        <v>6548988</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1877,27 +1902,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack med savflöde</t>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,31 +1923,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 47782-2025 artfynd.xlsx
+++ b/artfynd/A 47782-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -814,6 +819,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129405582</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129726348</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129726544</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129726545</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1254,6 +1279,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129726546</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1364,6 +1394,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129726547</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1474,6 +1509,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129726548</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129726549</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1694,6 +1739,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129726550</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1826,6 +1876,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129767860</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1936,8 +1991,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129726345</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>